--- a/Data/Withdrawal.xlsx
+++ b/Data/Withdrawal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eclipse\Desktop\Automation-Testing-2025\Eclipse\Automation\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F361EADE-F990-4A38-A185-164B24B4274A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A995C66-2F31-4E26-A786-1879B864DD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
   <si>
     <t>Withdrawal_Request_No</t>
   </si>
@@ -424,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -594,6 +594,29 @@
         <v>100</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>90904321</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>100673000000011</v>
+      </c>
+      <c r="F8" s="7">
+        <v>110001023651</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Data/Withdrawal.xlsx
+++ b/Data/Withdrawal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A995C66-2F31-4E26-A786-1879B864DD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA533C00-3DE2-41D8-9C53-0687D2AAEDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
   <si>
     <t>Withdrawal_Request_No</t>
   </si>
@@ -83,7 +83,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -93,6 +93,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -135,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -144,6 +150,10 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -595,25 +605,71 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="8">
         <v>90904321</v>
       </c>
-      <c r="B8" s="1">
-        <v>1000421</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5">
-        <v>100673000000011</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="B8" s="9">
+        <v>1000421</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10">
+        <v>100673000000011</v>
+      </c>
+      <c r="F8" s="11">
         <v>110001023651</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>9996065</v>
+      </c>
+      <c r="B9" s="9">
+        <v>1000421</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10">
+        <v>100673000000011</v>
+      </c>
+      <c r="F9" s="10">
+        <v>110001023677</v>
+      </c>
+      <c r="G9" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>9996066</v>
+      </c>
+      <c r="B10" s="9">
+        <v>1000421</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10">
+        <v>100673000000011</v>
+      </c>
+      <c r="F10" s="10">
+        <v>110001023776</v>
+      </c>
+      <c r="G10" s="8">
         <v>100</v>
       </c>
     </row>

--- a/Data/Withdrawal.xlsx
+++ b/Data/Withdrawal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA533C00-3DE2-41D8-9C53-0687D2AAEDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D849F3-DB12-4926-A988-E2718DA75F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
   <si>
     <t>Withdrawal_Request_No</t>
   </si>
@@ -83,7 +83,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -99,6 +99,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -141,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -154,6 +160,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -673,6 +683,29 @@
         <v>100</v>
       </c>
     </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <v>9996067</v>
+      </c>
+      <c r="B11" s="12">
+        <v>1000421</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="12">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13">
+        <v>100673001212128</v>
+      </c>
+      <c r="F11" s="14">
+        <v>110001031365</v>
+      </c>
+      <c r="G11" s="15">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Data/Withdrawal.xlsx
+++ b/Data/Withdrawal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D849F3-DB12-4926-A988-E2718DA75F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9B376C-AF7A-4597-845C-62A73BB56E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -93,12 +93,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -147,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -156,14 +150,13 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -453,7 +446,7 @@
     <col min="6" max="6" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -476,9 +469,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>9996059</v>
+        <v>9997359</v>
       </c>
       <c r="B2" s="1">
         <v>1000421</v>
@@ -487,21 +480,21 @@
         <v>4</v>
       </c>
       <c r="D2" s="1">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E2" s="5">
-        <v>100673000000011</v>
+        <v>100673001212128</v>
       </c>
       <c r="F2" s="5">
-        <v>110001018628</v>
+        <v>110001032660</v>
       </c>
       <c r="G2" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>9996060</v>
+        <v>9997263</v>
       </c>
       <c r="B3" s="1">
         <v>1000421</v>
@@ -510,21 +503,21 @@
         <v>4</v>
       </c>
       <c r="D3" s="1">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E3" s="5">
-        <v>100673000000011</v>
+        <v>100673001212128</v>
       </c>
       <c r="F3" s="5">
-        <v>110001023610</v>
+        <v>110001032686</v>
       </c>
       <c r="G3" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>9996061</v>
+        <v>9996063</v>
       </c>
       <c r="B4" s="1">
         <v>1000421</v>
@@ -545,9 +538,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>9996062</v>
+        <v>9994864</v>
       </c>
       <c r="B5" s="1">
         <v>1000421</v>
@@ -568,9 +561,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>9996063</v>
+        <v>9993665</v>
       </c>
       <c r="B6" s="1">
         <v>1000421</v>
@@ -591,9 +584,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>9996064</v>
+        <v>9992466</v>
       </c>
       <c r="B7" s="1">
         <v>1000421</v>
@@ -614,95 +607,98 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <v>90904321</v>
-      </c>
-      <c r="B8" s="9">
-        <v>1000421</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="9">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>9991267</v>
+      </c>
+      <c r="B8" s="8">
+        <v>1000421</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9">
         <v>100673000000011</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="13">
         <v>110001023651</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="12">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
-        <v>9996065</v>
-      </c>
-      <c r="B9" s="9">
-        <v>1000421</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="9">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10">
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>9990068</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1000421</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
         <v>100673000000011</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>110001023677</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="12">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
-        <v>9996066</v>
-      </c>
-      <c r="B10" s="9">
-        <v>1000421</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="9">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10">
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9988869</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1000421</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9">
         <v>100673000000011</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>110001023776</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="12">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
-        <v>9996067</v>
-      </c>
-      <c r="B11" s="12">
-        <v>1000421</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="12">
-        <v>1</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9987670</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1000421</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9">
         <v>100673001212128</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="10">
         <v>110001031365</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="11">
         <v>100</v>
       </c>
     </row>

--- a/Data/Withdrawal.xlsx
+++ b/Data/Withdrawal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9B376C-AF7A-4597-845C-62A73BB56E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D2A2B9-6404-46E8-B9CB-B2BAAA1D0120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,6 +81,12 @@
       <color rgb="FF2A314A"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A314A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -141,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -157,6 +163,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,9 +447,11 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -471,7 +480,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>9997359</v>
+        <v>9997361</v>
       </c>
       <c r="B2" s="1">
         <v>1000421</v>
@@ -480,21 +489,21 @@
         <v>4</v>
       </c>
       <c r="D2" s="1">
-        <v>6</v>
-      </c>
-      <c r="E2" s="5">
-        <v>100673001212128</v>
+        <v>15</v>
+      </c>
+      <c r="E2" s="15">
+        <v>120733340001420</v>
       </c>
       <c r="F2" s="5">
-        <v>110001032660</v>
+        <v>110001034930</v>
       </c>
       <c r="G2" s="4">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>9997263</v>
+        <v>9997272</v>
       </c>
       <c r="B3" s="1">
         <v>1000421</v>
@@ -503,21 +512,21 @@
         <v>4</v>
       </c>
       <c r="D3" s="1">
-        <v>49</v>
-      </c>
-      <c r="E3" s="5">
-        <v>100673001212128</v>
+        <v>15</v>
+      </c>
+      <c r="E3" s="15">
+        <v>120733340001420</v>
       </c>
       <c r="F3" s="5">
-        <v>110001032686</v>
+        <v>110001034914</v>
       </c>
       <c r="G3" s="4">
-        <v>780</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>9996063</v>
+        <v>9997163</v>
       </c>
       <c r="B4" s="1">
         <v>1000421</v>
@@ -526,13 +535,13 @@
         <v>4</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
-        <v>100673000000011</v>
+        <v>15</v>
+      </c>
+      <c r="E4" s="15">
+        <v>120733340001420</v>
       </c>
       <c r="F4" s="6">
-        <v>110001023651</v>
+        <v>110001034898</v>
       </c>
       <c r="G4" s="4">
         <v>100</v>
@@ -540,7 +549,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>9994864</v>
+        <v>9997064</v>
       </c>
       <c r="B5" s="1">
         <v>1000421</v>
@@ -549,13 +558,13 @@
         <v>4</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5">
-        <v>100673000000011</v>
+        <v>15</v>
+      </c>
+      <c r="E5" s="15">
+        <v>120733340001420</v>
       </c>
       <c r="F5" s="6">
-        <v>110001023677</v>
+        <v>110001034872</v>
       </c>
       <c r="G5" s="4">
         <v>100</v>
@@ -563,7 +572,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>9993665</v>
+        <v>9996965</v>
       </c>
       <c r="B6" s="1">
         <v>1000421</v>
@@ -572,10 +581,10 @@
         <v>4</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5">
-        <v>100673000000011</v>
+        <v>15</v>
+      </c>
+      <c r="E6" s="15">
+        <v>120733340001420</v>
       </c>
       <c r="F6" s="7">
         <v>110001023776</v>
@@ -586,7 +595,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>9992466</v>
+        <v>9996866</v>
       </c>
       <c r="B7" s="1">
         <v>1000421</v>
@@ -595,7 +604,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E7" s="5">
         <v>100673000000011</v>
@@ -609,7 +618,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>9991267</v>
+        <v>9996767</v>
       </c>
       <c r="B8" s="8">
         <v>1000421</v>
@@ -633,7 +642,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>9990068</v>
+        <v>9996668</v>
       </c>
       <c r="B9" s="8">
         <v>1000421</v>
@@ -657,7 +666,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9988869</v>
+        <v>9996569</v>
       </c>
       <c r="B10" s="8">
         <v>1000421</v>
@@ -681,7 +690,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>9987670</v>
+        <v>9996470</v>
       </c>
       <c r="B11" s="8">
         <v>1000421</v>

--- a/Data/Withdrawal.xlsx
+++ b/Data/Withdrawal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D2A2B9-6404-46E8-B9CB-B2BAAA1D0120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620706D7-A2E7-45EF-88A5-51560FAA8B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -587,10 +587,10 @@
         <v>120733340001420</v>
       </c>
       <c r="F6" s="7">
-        <v>110001023776</v>
+        <v>110001034815</v>
       </c>
       <c r="G6" s="4">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">

--- a/Data/Withdrawal.xlsx
+++ b/Data/Withdrawal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620706D7-A2E7-45EF-88A5-51560FAA8B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AB117C-B7F5-4DBE-A742-A11785F22B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/Withdrawal.xlsx
+++ b/Data/Withdrawal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AB117C-B7F5-4DBE-A742-A11785F22B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A53A8A-DA57-4225-B64C-2607CF397361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11040" yWindow="915" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Withdrawal_Request" sheetId="1" r:id="rId1"/>
@@ -572,25 +572,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>9996965</v>
+        <v>9996967</v>
       </c>
       <c r="B6" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="1">
-        <v>15</v>
-      </c>
-      <c r="E6" s="15">
-        <v>120733340001420</v>
+        <v>6</v>
+      </c>
+      <c r="E6" s="9">
+        <v>100673000000011</v>
       </c>
       <c r="F6" s="7">
-        <v>110001034815</v>
+        <v>110001035861</v>
       </c>
       <c r="G6" s="4">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">

--- a/Data/Withdrawal.xlsx
+++ b/Data/Withdrawal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A53A8A-DA57-4225-B64C-2607CF397361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B285435D-6255-4654-8472-2718A5E49FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11040" yWindow="915" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Withdrawal_Request" sheetId="1" r:id="rId1"/>
@@ -480,7 +480,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>9997361</v>
+        <v>180220262</v>
       </c>
       <c r="B2" s="1">
         <v>1000421</v>
@@ -489,16 +489,16 @@
         <v>4</v>
       </c>
       <c r="D2" s="1">
-        <v>15</v>
-      </c>
-      <c r="E2" s="15">
-        <v>120733340001420</v>
+        <v>6</v>
+      </c>
+      <c r="E2" s="9">
+        <v>100673001212128</v>
       </c>
       <c r="F2" s="5">
-        <v>110001034930</v>
+        <v>110001031324</v>
       </c>
       <c r="G2" s="4">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
